--- a/playwright-whatsapp-bot/contacts.xlsx
+++ b/playwright-whatsapp-bot/contacts.xlsx
@@ -30,10 +30,10 @@
     <t>Hi</t>
   </si>
   <si>
-    <t>Home.mithun.brother</t>
-  </si>
-  <si>
-    <t>Wife</t>
+    <t>1Home.mithun.brother</t>
+  </si>
+  <si>
+    <t>1Wife</t>
   </si>
 </sst>
 </file>
@@ -378,7 +378,7 @@
   <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="22" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="20.42578125" style="1" customWidth="1"/>
     <col min="3" max="3" width="13.85546875" customWidth="1"/>
   </cols>
@@ -399,7 +399,7 @@
         <v>4</v>
       </c>
       <c r="B2" s="1">
-        <v>9080034010</v>
+        <v>9080012345</v>
       </c>
       <c r="C2" t="s">
         <v>3</v>
@@ -410,7 +410,7 @@
         <v>5</v>
       </c>
       <c r="B3" s="1">
-        <v>9952308596</v>
+        <v>9952354321</v>
       </c>
       <c r="C3" t="s">
         <v>3</v>
